--- a/reports/Debug-purgatory-20260106/Month to Date (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260106/Month to Date (Prior Year)_Revenue.xlsx
@@ -106,16 +106,16 @@
     <t>T103</t>
   </si>
   <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T101</t>
   </si>
   <si>
-    <t>T100</t>
+    <t>T104</t>
   </si>
   <si>
     <t>T105</t>
-  </si>
-  <si>
-    <t>T104</t>
   </si>
   <si>
     <t>department</t>
@@ -613,7 +613,7 @@
         <v>35</v>
       </c>
       <c r="D3" s="2">
-        <v>6167.42</v>
+        <v>491980.56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -627,7 +627,7 @@
         <v>35</v>
       </c>
       <c r="D4" s="2">
-        <v>491980.56</v>
+        <v>6167.42</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -641,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="D5" s="2">
-        <v>5626.00</v>
+        <v>69.50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -655,7 +655,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="2">
-        <v>69.50</v>
+        <v>5626.00</v>
       </c>
     </row>
     <row r="7" spans="1:4">
